--- a/sheets/조재수대금교본/검수/아침이슬.xlsx
+++ b/sheets/조재수대금교본/검수/아침이슬.xlsx
@@ -4915,17 +4915,9 @@
         </is>
       </c>
       <c r="C9" s="23"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="23"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="23"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
@@ -4935,16 +4927,11 @@
       <c r="I9" s="23"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K9" s="23"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="23"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
@@ -4952,11 +4939,7 @@
         </is>
       </c>
       <c r="O9" s="23"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
     </row>
     <row r="10" ht="68.7" customHeight="true">
@@ -5302,43 +5285,19 @@
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D17" s="21"/>
       <c r="E17" s="23"/>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F17" s="21"/>
       <c r="G17" s="23"/>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H17" s="21"/>
       <c r="I17" s="23"/>
       <c r="J17" s="21"/>
       <c r="K17" s="23"/>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L17" s="21"/>
       <c r="M17" s="23"/>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N17" s="21"/>
       <c r="O17" s="23"/>
-      <c r="P17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P17" s="21"/>
       <c r="Q17" s="23"/>
     </row>
     <row r="18" ht="68.7" customHeight="true">
@@ -5358,7 +5317,7 @@
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–И</t>
+–</t>
         </is>
       </c>
       <c r="G18" s="24"/>

--- a/sheets/조재수대금교본/검수/아침이슬.xlsx
+++ b/sheets/조재수대금교본/검수/아침이슬.xlsx
@@ -5317,7 +5317,7 @@
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–</t>
+–И</t>
         </is>
       </c>
       <c r="G18" s="24"/>

--- a/sheets/조재수대금교본/검수/아침이슬.xlsx
+++ b/sheets/조재수대금교본/검수/아침이슬.xlsx
@@ -4556,28 +4556,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="61.54" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="68.7" customHeight="true">
+    <row r="3" ht="72.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="68.7" customHeight="true">
+    <row r="4" ht="72.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="68.7" customHeight="true">
+    <row r="5" ht="72.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" ht="68.7" customHeight="true">
+    <row r="6" ht="72.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="68.7" customHeight="true">
+    <row r="7" ht="72.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="68.7" customHeight="true">
+    <row r="8" ht="72.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="68.7" customHeight="true">
+    <row r="9" ht="72.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="68.7" customHeight="true">
+    <row r="10" ht="72.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" ht="68.7" customHeight="true">
+    <row r="11" ht="72.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="68.7" customHeight="true">
+    <row r="12" ht="72.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Q12" s="23"/>
     </row>
-    <row r="13" ht="68.7" customHeight="true">
+    <row r="13" ht="72.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="68.7" customHeight="true">
+    <row r="14" ht="72.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="Q14" s="24"/>
     </row>
-    <row r="15" ht="68.7" customHeight="true">
+    <row r="15" ht="72.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" ht="68.7" customHeight="true">
+    <row r="16" ht="72.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5281,7 +5281,7 @@
       <c r="P16" s="21"/>
       <c r="Q16" s="23"/>
     </row>
-    <row r="17" ht="68.7" customHeight="true">
+    <row r="17" ht="72.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5300,7 +5300,7 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="23"/>
     </row>
-    <row r="18" ht="68.7" customHeight="true">
+    <row r="18" ht="72.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5355,6 +5355,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>